--- a/water-angel-ml/Water_Angel_ML_Features_and_Predictions.xlsx
+++ b/water-angel-ml/Water_Angel_ML_Features_and_Predictions.xlsx
@@ -26698,7 +26698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -26829,6 +26829,82 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aaaaaaaa-1111-1111-1111-aaaaaaaaaaaa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>weekly_consumption</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ridge-weekly-v1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>978.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Written to Supabase (Dynamic ML: -21.8L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bbbbbbbb-2222-2222-2222-bbbbbbbbbbbb</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>weekly_consumption</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ridge-weekly-v1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>987.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Written to Supabase (Dynamic ML: -12.2L)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
